--- a/data/Experiment/Raw/Spreadsheets/TheWorks_09052025.xlsx
+++ b/data/Experiment/Raw/Spreadsheets/TheWorks_09052025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10830"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10110"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/fernbromley/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/fernbromley/Desktop/SeedlingMortality/data/Experiment/Raw/Spreadsheets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A64196E0-48A7-724B-9045-CD59C3AEDFE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB0B31A1-D83A-8246-8325-B998C1210749}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10020" yWindow="760" windowWidth="19380" windowHeight="17120" activeTab="1" xr2:uid="{CA551DF1-0ED1-674A-8F89-05216640288A}"/>
+    <workbookView xWindow="20" yWindow="800" windowWidth="13560" windowHeight="17120" xr2:uid="{CA551DF1-0ED1-674A-8F89-05216640288A}"/>
   </bookViews>
   <sheets>
     <sheet name="PIFL" sheetId="2" r:id="rId1"/>
@@ -844,7 +844,7 @@
         <v>5</v>
       </c>
       <c r="B4">
-        <v>246.5</v>
+        <v>346.5</v>
       </c>
       <c r="C4" s="4">
         <v>0.1</v>
